--- a/Result/profitability/1583.xlsx
+++ b/Result/profitability/1583.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.64</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6925</v>
+        <v>0.5462500000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>19.435</v>
+        <v>19.6125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.28</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6625000000000001</v>
+        <v>-0.2899999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>20.76375</v>
+        <v>20.91625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.83</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1049999999999999</v>
+        <v>0.8625</v>
       </c>
       <c r="N4" t="n">
-        <v>22.385</v>
+        <v>22.35</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-1.9</v>
       </c>
       <c r="M5" t="n">
-        <v>0.58125</v>
+        <v>0.7800000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>22.83125</v>
+        <v>23.315</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.06</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7287500000000001</v>
+        <v>0.4062500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>23.70625</v>
+        <v>23.9825</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3637500000000001</v>
+        <v>0.29125</v>
       </c>
       <c r="N7" t="n">
-        <v>24.44</v>
+        <v>24.4425</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.23</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2762500000000001</v>
+        <v>0.2975</v>
       </c>
       <c r="N8" t="n">
-        <v>24.5875</v>
+        <v>24.79375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>0.32</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2362500000000001</v>
+        <v>0.23625</v>
       </c>
       <c r="N10" t="n">
         <v>24.76125</v>
@@ -1772,7 +1772,7 @@
         <v>0.66</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1587500000000001</v>
+        <v>0.15875</v>
       </c>
       <c r="N11" t="n">
         <v>24.45125</v>
@@ -1899,7 +1899,7 @@
         <v>0.85</v>
       </c>
       <c r="M12" t="n">
-        <v>0.03625000000000005</v>
+        <v>0.03625000000000002</v>
       </c>
       <c r="N12" t="n">
         <v>24.20125</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1583</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1044</v>
+      </c>
+      <c r="D75" t="n">
+        <v>839</v>
+      </c>
+      <c r="E75" t="n">
+        <v>206</v>
+      </c>
+      <c r="F75" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-21</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-1.99%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>64</v>
+      </c>
+      <c r="J75" t="n">
+        <v>43</v>
+      </c>
+      <c r="K75" t="n">
+        <v>38</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.65625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>18.41625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.649999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.09151414309484185</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.282258064516129</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.869999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2447817836812143</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
